--- a/03-Renewable-Energy-Project/Renewable Energy Solar Financial Model.xlsx
+++ b/03-Renewable-Energy-Project/Renewable Energy Solar Financial Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\finance-portfolio\03-Renewable-Energy-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D70339-26DC-4B4D-AB61-73DFC808C4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2286BBC7-D5A9-4511-8FBB-6AFFC9FEE67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -933,7 +933,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -1461,6 +1461,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -11340,7 +11343,7 @@
         <v>28</v>
       </c>
       <c r="G82" s="103">
-        <f t="dataTable" ref="G82:AJ82" dt2D="0" dtr="0" r1="G10"/>
+        <f t="dataTable" ref="G82:AJ82" dt2D="0" dtr="0" r1="G10" ca="1"/>
         <v>2385210.75</v>
       </c>
       <c r="H82" s="103">
@@ -19291,9 +19294,9 @@
       <c r="B179" s="18"/>
       <c r="C179" s="18"/>
       <c r="D179" s="19"/>
-      <c r="F179" s="155" t="e">
-        <f>XNPV(J31,F175:AJ175,F2:K2)</f>
-        <v>#NUM!</v>
+      <c r="F179" s="232">
+        <f>XNPV(J31,F175:AJ175,F2:AJ2)</f>
+        <v>1794115.492594932</v>
       </c>
     </row>
     <row r="180" spans="1:36" s="20" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -20036,7 +20039,7 @@
         <v>50</v>
       </c>
       <c r="H206" s="215">
-        <f t="dataTable" ref="H206:L213" dt2D="1" dtr="1" r1="P17" r2="R17" ca="1"/>
+        <f t="dataTable" ref="H206:L213" dt2D="1" dtr="1" r1="P17" r2="R17"/>
         <v>9.8677708551443519</v>
       </c>
       <c r="I206" s="215">
